--- a/journal_dataset.xlsx
+++ b/journal_dataset.xlsx
@@ -4,16 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="13000" windowHeight="6200" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="editor workload" sheetId="2" r:id="rId1"/>
-    <sheet name="decision distribution" sheetId="3" r:id="rId2"/>
-    <sheet name="workflow_data" sheetId="1" r:id="rId3"/>
+    <sheet name="editor KPI" sheetId="6" r:id="rId1"/>
+    <sheet name="workflow_data" sheetId="1" r:id="rId2"/>
+    <sheet name="editor workload" sheetId="2" r:id="rId3"/>
+    <sheet name="decision distribution" sheetId="4" r:id="rId4"/>
+    <sheet name="review performance metrics" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,12 +35,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="43">
   <si>
     <t>editor</t>
   </si>
   <si>
-    <t>Count of manuscript_id</t>
+    <t>Average of TAT_days</t>
   </si>
   <si>
     <t>Editor A</t>
@@ -50,18 +53,6 @@
   </si>
   <si>
     <t>Grand Total</t>
-  </si>
-  <si>
-    <t>decision</t>
-  </si>
-  <si>
-    <t>Major Revision</t>
-  </si>
-  <si>
-    <t>Minor Revision</t>
-  </si>
-  <si>
-    <t>Reject</t>
   </si>
   <si>
     <t>Editor assigment time: 1-2 days</t>
@@ -91,13 +82,31 @@
     <t>decision_date</t>
   </si>
   <si>
+    <t>decision</t>
+  </si>
+  <si>
+    <t>review_duration_days</t>
+  </si>
+  <si>
+    <t>TAT_days</t>
+  </si>
+  <si>
     <t>M001</t>
+  </si>
+  <si>
+    <t>Minor Revision</t>
   </si>
   <si>
     <t>M002</t>
   </si>
   <si>
+    <t>Reject</t>
+  </si>
+  <si>
     <t>M003</t>
+  </si>
+  <si>
+    <t>Major Revision</t>
   </si>
   <si>
     <t>M004</t>
@@ -150,6 +159,12 @@
   <si>
     <t>M020</t>
   </si>
+  <si>
+    <t>Count of manuscript_id</t>
+  </si>
+  <si>
+    <t>Average of review_duration_days</t>
+  </si>
 </sst>
 </file>
 
@@ -161,7 +176,14 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -634,16 +656,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -652,122 +671,126 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
@@ -1046,12 +1069,2935 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[journal_dataset.xlsx]editor KPI!PivotTable6</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'editor KPI'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="1"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'editor KPI'!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Editor A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Editor B</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Editor C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'editor KPI'!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>18.8571428571429</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.1428571428571</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="751358296"/>
+        <c:axId val="973604241"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="751358296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973604241"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="973604241"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="751358296"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[journal_dataset.xlsx]decision distribution!PivotTable4</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'decision distribution'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr/>
+          <c:explosion val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="1"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'decision distribution'!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Major Revision</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Minor Revision</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Reject</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'decision distribution'!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[journal_dataset.xlsx]review performance metrics!PivotTable5</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'review performance metrics'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="1"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'review performance metrics'!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Editor A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Editor B</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Editor C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'review performance metrics'!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>16.8571428571429</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18.7142857142857</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="603487622"/>
+        <c:axId val="93748664"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="603487622"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="93748664"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="93748664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="603487622"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>387350</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="2654300" y="387350"/>
+        <a:ext cx="4826000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>577850</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3232150" y="533400"/>
+        <a:ext cx="4826000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3270250" y="558800"/>
+        <a:ext cx="4826000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46092.6266435185" refreshedBy="USER" recordCount="20">
   <cacheSource type="worksheet">
     <worksheetSource ref="B3:I23" sheet="workflow_data"/>
   </cacheSource>
   <cacheFields count="8">
+    <cacheField name="manuscript_id" numFmtId="0">
+      <sharedItems count="20">
+        <s v="M001"/>
+        <s v="M002"/>
+        <s v="M003"/>
+        <s v="M004"/>
+        <s v="M005"/>
+        <s v="M006"/>
+        <s v="M007"/>
+        <s v="M008"/>
+        <s v="M009"/>
+        <s v="M010"/>
+        <s v="M011"/>
+        <s v="M012"/>
+        <s v="M013"/>
+        <s v="M014"/>
+        <s v="M015"/>
+        <s v="M016"/>
+        <s v="M017"/>
+        <s v="M018"/>
+        <s v="M019"/>
+        <s v="M020"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="submission_date" numFmtId="58">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNonDate="0" containsDate="1" minDate="2026-01-02T00:00:00" maxDate="2026-01-21T00:00:00" count="20">
+        <d v="2026-01-02T00:00:00"/>
+        <d v="2026-01-03T00:00:00"/>
+        <d v="2026-01-04T00:00:00"/>
+        <d v="2026-01-05T00:00:00"/>
+        <d v="2026-01-06T00:00:00"/>
+        <d v="2026-01-07T00:00:00"/>
+        <d v="2026-01-08T00:00:00"/>
+        <d v="2026-01-09T00:00:00"/>
+        <d v="2026-01-10T00:00:00"/>
+        <d v="2026-01-11T00:00:00"/>
+        <d v="2026-01-12T00:00:00"/>
+        <d v="2026-01-13T00:00:00"/>
+        <d v="2026-01-14T00:00:00"/>
+        <d v="2026-01-15T00:00:00"/>
+        <d v="2026-01-16T00:00:00"/>
+        <d v="2026-01-17T00:00:00"/>
+        <d v="2026-01-18T00:00:00"/>
+        <d v="2026-01-19T00:00:00"/>
+        <d v="2026-01-20T00:00:00"/>
+        <d v="2026-01-21T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="editor_assignment_date" numFmtId="58">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNonDate="0" containsDate="1" minDate="2026-01-03T00:00:00" maxDate="2026-01-22T00:00:00" count="16">
+        <d v="2026-01-03T00:00:00"/>
+        <d v="2026-01-04T00:00:00"/>
+        <d v="2026-01-06T00:00:00"/>
+        <d v="2026-01-07T00:00:00"/>
+        <d v="2026-01-09T00:00:00"/>
+        <d v="2026-01-10T00:00:00"/>
+        <d v="2026-01-11T00:00:00"/>
+        <d v="2026-01-12T00:00:00"/>
+        <d v="2026-01-13T00:00:00"/>
+        <d v="2026-01-15T00:00:00"/>
+        <d v="2026-01-16T00:00:00"/>
+        <d v="2026-01-17T00:00:00"/>
+        <d v="2026-01-18T00:00:00"/>
+        <d v="2026-01-20T00:00:00"/>
+        <d v="2026-01-21T00:00:00"/>
+        <d v="2026-01-22T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="reviewer_count" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3" count="2">
+        <n v="2"/>
+        <n v="3"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="review_complete_date" numFmtId="58">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNonDate="0" containsDate="1" minDate="2026-01-18T00:00:00" maxDate="2026-02-10T00:00:00" count="20">
+        <d v="2026-01-18T00:00:00"/>
+        <d v="2026-01-21T00:00:00"/>
+        <d v="2026-01-25T00:00:00"/>
+        <d v="2026-01-20T00:00:00"/>
+        <d v="2026-01-23T00:00:00"/>
+        <d v="2026-01-24T00:00:00"/>
+        <d v="2026-01-26T00:00:00"/>
+        <d v="2026-01-28T00:00:00"/>
+        <d v="2026-01-29T00:00:00"/>
+        <d v="2026-01-27T00:00:00"/>
+        <d v="2026-01-30T00:00:00"/>
+        <d v="2026-02-02T00:00:00"/>
+        <d v="2026-02-01T00:00:00"/>
+        <d v="2026-02-03T00:00:00"/>
+        <d v="2026-02-05T00:00:00"/>
+        <d v="2026-02-04T00:00:00"/>
+        <d v="2026-02-07T00:00:00"/>
+        <d v="2026-02-08T00:00:00"/>
+        <d v="2026-02-06T00:00:00"/>
+        <d v="2026-02-10T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="decision_date" numFmtId="58">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNonDate="0" containsDate="1" minDate="2026-01-20T00:00:00" maxDate="2026-02-12T00:00:00" count="18">
+        <d v="2026-01-20T00:00:00"/>
+        <d v="2026-01-24T00:00:00"/>
+        <d v="2026-01-27T00:00:00"/>
+        <d v="2026-01-22T00:00:00"/>
+        <d v="2026-01-25T00:00:00"/>
+        <d v="2026-01-28T00:00:00"/>
+        <d v="2026-01-30T00:00:00"/>
+        <d v="2026-02-01T00:00:00"/>
+        <d v="2026-01-29T00:00:00"/>
+        <d v="2026-02-02T00:00:00"/>
+        <d v="2026-02-05T00:00:00"/>
+        <d v="2026-02-03T00:00:00"/>
+        <d v="2026-02-06T00:00:00"/>
+        <d v="2026-02-07T00:00:00"/>
+        <d v="2026-02-09T00:00:00"/>
+        <d v="2026-02-10T00:00:00"/>
+        <d v="2026-02-08T00:00:00"/>
+        <d v="2026-02-12T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="decision" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Minor Revision"/>
+        <s v="Reject"/>
+        <s v="Major Revision"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="editor" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Editor A"/>
+        <s v="Editor B"/>
+        <s v="Editor C"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46098.5599652778" refreshedBy="USER" recordCount="20">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="B3:K23" sheet="workflow_data"/>
+  </cacheSource>
+  <cacheFields count="10">
     <cacheField name="manuscript_id" numFmtId="0">
       <sharedItems count="20">
         <s v="M001"/>
@@ -1186,6 +4132,28 @@
         <s v="Editor C"/>
       </sharedItems>
     </cacheField>
+    <cacheField name="review_duration_days" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15" maxValue="21" count="7">
+        <n v="16"/>
+        <n v="18"/>
+        <n v="21"/>
+        <n v="15"/>
+        <n v="17"/>
+        <n v="19"/>
+        <n v="20"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="TAT_days" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="17" maxValue="23" count="7">
+        <n v="18"/>
+        <n v="21"/>
+        <n v="23"/>
+        <n v="17"/>
+        <n v="19"/>
+        <n v="20"/>
+        <n v="22"/>
+      </sharedItems>
+    </cacheField>
   </cacheFields>
 </pivotCacheDefinition>
 </file>
@@ -1395,63 +4363,256 @@
 </pivotCacheRecords>
 </file>
 
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField dataField="1" compact="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="58" showAll="0"/>
-    <pivotField compact="0" numFmtId="58" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="58" showAll="0"/>
-    <pivotField compact="0" numFmtId="58" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of manuscript_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="20">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="10"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="11"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="6"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="12"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="14"/>
+    <x v="11"/>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="13"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="6"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="15"/>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="16"/>
+    <x v="13"/>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="14"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="17"/>
+    <x v="13"/>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="15"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="6"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="18"/>
+    <x v="14"/>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="16"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="19"/>
+    <x v="15"/>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="6"/>
+  </r>
+</pivotCacheRecords>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="1" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField dataField="1" compact="0" showAll="0">
+  <pivotFields count="10">
+    <pivotField compact="0" showAll="0">
       <items count="21">
         <item x="0"/>
         <item x="1"/>
@@ -1577,6 +4738,165 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField compact="0" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of TAT_days" fld="9" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField dataField="1" compact="0" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="58" showAll="0"/>
+    <pivotField compact="0" numFmtId="58" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="58" showAll="0"/>
+    <pivotField compact="0" numFmtId="58" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of manuscript_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="1" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField dataField="1" compact="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="58" showAll="0"/>
+    <pivotField compact="0" numFmtId="58" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="58" showAll="0"/>
+    <pivotField compact="0" numFmtId="58" showAll="0"/>
     <pivotField axis="axisRow" compact="0" showAll="0">
       <items count="4">
         <item x="2"/>
@@ -1585,14 +4905,9 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="6"/>
@@ -1616,6 +4931,209 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Count of manuscript_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="1" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField compact="0" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="58" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="58" showAll="0">
+      <items count="17">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="58" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="58" showAll="0">
+      <items count="19">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of review_duration_days" fld="8" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1"/>
   <extLst>
@@ -1888,7 +5406,7 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="11.6363636363636"/>
-    <col min="2" max="2" width="22.7272727272727"/>
+    <col min="2" max="2" width="20.0909090909091"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2">
@@ -1904,7 +5422,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>18.8571428571429</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1912,7 +5430,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>21.1428571428571</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1920,7 +5438,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1928,7 +5446,712 @@
         <v>5</v>
       </c>
       <c r="B7">
+        <v>20.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:K23"/>
+  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="13.9090909090909" customWidth="1"/>
+    <col min="3" max="3" width="16.3636363636364" customWidth="1"/>
+    <col min="4" max="4" width="23.2727272727273" customWidth="1"/>
+    <col min="5" max="5" width="15.1818181818182" customWidth="1"/>
+    <col min="6" max="6" width="21.9090909090909" customWidth="1"/>
+    <col min="7" max="7" width="13.5454545454545" customWidth="1"/>
+    <col min="8" max="8" width="14.5454545454545" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:11">
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46024</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46040</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46042</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1">
+        <v>16</v>
+      </c>
+      <c r="K4" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" t="s">
         <v>20</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46025</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46026</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46043</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46046</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1">
+        <v>18</v>
+      </c>
+      <c r="K5" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46026</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46028</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46047</v>
+      </c>
+      <c r="G6" s="2">
+        <v>46049</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" s="1">
+        <v>21</v>
+      </c>
+      <c r="K6" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46027</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46028</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46042</v>
+      </c>
+      <c r="G7" s="2">
+        <v>46044</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1">
+        <v>15</v>
+      </c>
+      <c r="K7" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46028</v>
+      </c>
+      <c r="D8" s="2">
+        <v>46029</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46045</v>
+      </c>
+      <c r="G8" s="2">
+        <v>46047</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="1">
+        <v>17</v>
+      </c>
+      <c r="K8" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46029</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46031</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46046</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46049</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="1">
+        <v>17</v>
+      </c>
+      <c r="K9" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46030</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46031</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>46048</v>
+      </c>
+      <c r="G10" s="2">
+        <v>46050</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="1">
+        <v>18</v>
+      </c>
+      <c r="K10" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46031</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46032</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>46050</v>
+      </c>
+      <c r="G11" s="2">
+        <v>46052</v>
+      </c>
+      <c r="H11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="1">
+        <v>19</v>
+      </c>
+      <c r="K11" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46032</v>
+      </c>
+      <c r="D12" s="2">
+        <v>46033</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>46051</v>
+      </c>
+      <c r="G12" s="2">
+        <v>46054</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="1">
+        <v>19</v>
+      </c>
+      <c r="K12" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46033</v>
+      </c>
+      <c r="D13" s="2">
+        <v>46034</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>46049</v>
+      </c>
+      <c r="G13" s="2">
+        <v>46051</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1">
+        <v>16</v>
+      </c>
+      <c r="K13" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46034</v>
+      </c>
+      <c r="D14" s="2">
+        <v>46035</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>46052</v>
+      </c>
+      <c r="G14" s="2">
+        <v>46055</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="1">
+        <v>18</v>
+      </c>
+      <c r="K14" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46035</v>
+      </c>
+      <c r="D15" s="2">
+        <v>46037</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>46055</v>
+      </c>
+      <c r="G15" s="2">
+        <v>46058</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="1">
+        <v>20</v>
+      </c>
+      <c r="K15" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46036</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46037</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G16" s="2">
+        <v>46056</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="1">
+        <v>18</v>
+      </c>
+      <c r="K16" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2">
+        <v>46037</v>
+      </c>
+      <c r="D17" s="2">
+        <v>46038</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>46056</v>
+      </c>
+      <c r="G17" s="2">
+        <v>46059</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="1">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46038</v>
+      </c>
+      <c r="D18" s="2">
+        <v>46039</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G18" s="2">
+        <v>46060</v>
+      </c>
+      <c r="H18" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="1">
+        <v>20</v>
+      </c>
+      <c r="K18" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="2">
+        <v>46039</v>
+      </c>
+      <c r="D19" s="2">
+        <v>46040</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G19" s="2">
+        <v>46059</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" s="1">
+        <v>18</v>
+      </c>
+      <c r="K19" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2">
+        <v>46040</v>
+      </c>
+      <c r="D20" s="2">
+        <v>46042</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>46060</v>
+      </c>
+      <c r="G20" s="2">
+        <v>46062</v>
+      </c>
+      <c r="H20" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1">
+        <v>20</v>
+      </c>
+      <c r="K20" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="2">
+        <v>46041</v>
+      </c>
+      <c r="D21" s="2">
+        <v>46042</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>46061</v>
+      </c>
+      <c r="G21" s="2">
+        <v>46063</v>
+      </c>
+      <c r="H21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="1">
+        <v>20</v>
+      </c>
+      <c r="K21" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="2">
+        <v>46042</v>
+      </c>
+      <c r="D22" s="2">
+        <v>46043</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2">
+        <v>46059</v>
+      </c>
+      <c r="G22" s="2">
+        <v>46061</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" t="s">
+        <v>2</v>
+      </c>
+      <c r="J22" s="1">
+        <v>17</v>
+      </c>
+      <c r="K22" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="2">
+        <v>46043</v>
+      </c>
+      <c r="D23" s="2">
+        <v>46044</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G23" s="2">
+        <v>46065</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="1">
+        <v>20</v>
+      </c>
+      <c r="K23" s="1">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1937,7 +6160,63 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3:B7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="11.6363636363636"/>
+    <col min="2" max="2" width="22.7272727272727"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A3:B7"/>
@@ -1949,15 +6228,15 @@
   <sheetData>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -1965,7 +6244,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -1973,7 +6252,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -1990,583 +6269,63 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:I23"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14.5"/>
+  <dimension ref="A3:B7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="1"/>
   <cols>
-    <col min="2" max="2" width="13.9090909090909" customWidth="1"/>
-    <col min="3" max="3" width="16.3636363636364" customWidth="1"/>
-    <col min="4" max="4" width="23.2727272727273" customWidth="1"/>
-    <col min="5" max="5" width="15.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="21.9090909090909" customWidth="1"/>
-    <col min="7" max="7" width="13.5454545454545" customWidth="1"/>
-    <col min="8" max="8" width="14.5454545454545" customWidth="1"/>
+    <col min="1" max="1" width="11.6363636363636"/>
+    <col min="2" max="2" width="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9">
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="3" spans="2:9">
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" t="s">
-        <v>0</v>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>16.8571428571429</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1">
-        <v>46024</v>
-      </c>
-      <c r="D4" s="1">
-        <v>46025</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4" s="1">
-        <v>46040</v>
-      </c>
-      <c r="G4" s="1">
-        <v>46042</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>2</v>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>18.7142857142857</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1">
-        <v>46025</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46026</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1">
-        <v>46043</v>
-      </c>
-      <c r="G5" s="1">
-        <v>46046</v>
-      </c>
-      <c r="H5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" t="s">
-        <v>3</v>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>19.5</v>
       </c>
     </row>
-    <row r="6" spans="2:9">
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46026</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46028</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46047</v>
-      </c>
-      <c r="G6" s="1">
-        <v>46049</v>
-      </c>
-      <c r="H6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="1">
-        <v>46027</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46028</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46042</v>
-      </c>
-      <c r="G7" s="1">
-        <v>46044</v>
-      </c>
-      <c r="H7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1">
-        <v>46028</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46029</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46045</v>
-      </c>
-      <c r="G8" s="1">
-        <v>46047</v>
-      </c>
-      <c r="H8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1">
-        <v>46029</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46031</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1">
-        <v>46046</v>
-      </c>
-      <c r="G9" s="1">
-        <v>46049</v>
-      </c>
-      <c r="H9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1">
-        <v>46030</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46031</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46048</v>
-      </c>
-      <c r="G10" s="1">
-        <v>46050</v>
-      </c>
-      <c r="H10" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1">
-        <v>46031</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46032</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46050</v>
-      </c>
-      <c r="G11" s="1">
-        <v>46052</v>
-      </c>
-      <c r="H11" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9">
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="1">
-        <v>46032</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46033</v>
-      </c>
-      <c r="E12">
-        <v>3</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46051</v>
-      </c>
-      <c r="G12" s="1">
-        <v>46054</v>
-      </c>
-      <c r="H12" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="1">
-        <v>46033</v>
-      </c>
-      <c r="D13" s="1">
-        <v>46034</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46049</v>
-      </c>
-      <c r="G13" s="1">
-        <v>46051</v>
-      </c>
-      <c r="H13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="1">
-        <v>46034</v>
-      </c>
-      <c r="D14" s="1">
-        <v>46035</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46052</v>
-      </c>
-      <c r="G14" s="1">
-        <v>46055</v>
-      </c>
-      <c r="H14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="1">
-        <v>46035</v>
-      </c>
-      <c r="D15" s="1">
-        <v>46037</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15" s="1">
-        <v>46055</v>
-      </c>
-      <c r="G15" s="1">
-        <v>46058</v>
-      </c>
-      <c r="H15" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="1">
-        <v>46036</v>
-      </c>
-      <c r="D16" s="1">
-        <v>46037</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16" s="1">
-        <v>46054</v>
-      </c>
-      <c r="G16" s="1">
-        <v>46056</v>
-      </c>
-      <c r="H16" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="1">
-        <v>46037</v>
-      </c>
-      <c r="D17" s="1">
-        <v>46038</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46056</v>
-      </c>
-      <c r="G17" s="1">
-        <v>46059</v>
-      </c>
-      <c r="H17" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="1">
-        <v>46038</v>
-      </c>
-      <c r="D18" s="1">
-        <v>46039</v>
-      </c>
-      <c r="E18">
-        <v>3</v>
-      </c>
-      <c r="F18" s="1">
-        <v>46058</v>
-      </c>
-      <c r="G18" s="1">
-        <v>46060</v>
-      </c>
-      <c r="H18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="1">
-        <v>46039</v>
-      </c>
-      <c r="D19" s="1">
-        <v>46040</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
-      <c r="F19" s="1">
-        <v>46057</v>
-      </c>
-      <c r="G19" s="1">
-        <v>46059</v>
-      </c>
-      <c r="H19" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="1">
-        <v>46040</v>
-      </c>
-      <c r="D20" s="1">
-        <v>46042</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20" s="1">
-        <v>46060</v>
-      </c>
-      <c r="G20" s="1">
-        <v>46062</v>
-      </c>
-      <c r="H20" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="1">
-        <v>46041</v>
-      </c>
-      <c r="D21" s="1">
-        <v>46042</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46061</v>
-      </c>
-      <c r="G21" s="1">
-        <v>46063</v>
-      </c>
-      <c r="H21" t="s">
-        <v>7</v>
-      </c>
-      <c r="I21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="1">
-        <v>46042</v>
-      </c>
-      <c r="D22" s="1">
-        <v>46043</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
-      <c r="F22" s="1">
-        <v>46059</v>
-      </c>
-      <c r="G22" s="1">
-        <v>46061</v>
-      </c>
-      <c r="H22" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="1">
-        <v>46043</v>
-      </c>
-      <c r="D23" s="1">
-        <v>46044</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23" s="1">
-        <v>46063</v>
-      </c>
-      <c r="G23" s="1">
-        <v>46065</v>
-      </c>
-      <c r="H23" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" t="s">
-        <v>3</v>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>18.3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>